--- a/output_test/data_catalog.xlsx
+++ b/output_test/data_catalog.xlsx
@@ -919,7 +919,7 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
@@ -1040,12 +1040,16 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1, 2, 3, 4, 5</t>
+          <t>Auto-Increment</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="N2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1">
@@ -1090,15 +1094,19 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>CB001, CB002, CB003, CB004, CB005</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>MaCanBo</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -1136,14 +1144,14 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Văn An, Trần Thị Bình, Lê Văn Cường, Phạm Thị Dung, Hoàng Văn Em</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Họ và tên</t>
+          <t>HoTen</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr"/>
@@ -1184,12 +1192,16 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Ngày sinh</t>
+          <t>NgaySinh</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
@@ -1219,7 +1231,11 @@
           <t>enum</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Có</t>
@@ -1235,12 +1251,12 @@
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Giới tính</t>
+          <t>GioiTinh</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -1278,19 +1294,19 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>038075003124, 038080007256, 038085011342, 038090002198, 038088009276</t>
+          <t>Chuỗi 12 chữ số</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Căn cước công dân</t>
+          <t>SoDinhDanh</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -1328,19 +1344,19 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0912345678, 0923456789, 0934567890, 0945678901, 0956789012</t>
+          <t>Số điện thoại</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Số điện thoại</t>
+          <t>SoDienThoai</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -1378,7 +1394,7 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>an@gmail.com, binh@gmail.com, cuong@gmail.com, dung@gmail.com, em@gmail.com</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
@@ -1432,12 +1448,16 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3, 7, 2, 5, 6, 4, 1</t>
+          <t>Map với dm_don_vi</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>MaCoQuan</t>
+        </is>
+      </c>
       <c r="N10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1478,12 +1498,16 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>GD, PGD, TP, CV</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>MaChucDanh</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1511,7 +1535,11 @@
           <t>enum</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Có</t>
@@ -1525,10 +1553,14 @@
       </c>
       <c r="K12" s="3" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>TrinhDo</t>
+        </is>
+      </c>
       <c r="N12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1566,12 +1598,16 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Quản lý đất đai, Môi trường, Địa chính, Luật đất đai, Khoáng sản</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>ChuyenNganh</t>
+        </is>
+      </c>
       <c r="N13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1610,10 +1646,18 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>NgayVao</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -1654,14 +1698,14 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1, 0</t>
+          <t>0: Nghỉ, 1: Đang làm</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái</t>
+          <t>TrangThai</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
@@ -1702,10 +1746,18 @@
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>LuongCanBo</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1744,10 +1796,18 @@
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>UpdatedAt</t>
+        </is>
+      </c>
       <c r="N17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1792,12 +1852,16 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5, 1, 6, 2, 4, 3</t>
+          <t>Auto-Increment</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="N18" s="3" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1842,15 +1906,19 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>CV, GD, NV, PGD, PP, TP</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -1888,14 +1956,14 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Giám đốc, Phó Giám đốc, Trưởng phòng, Phó phòng, Chuyên viên, Nhân viên</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr"/>
       <c r="L20" s="3" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Họ và tên</t>
+          <t>Ten</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -1938,12 +2006,16 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8, 7, 6, 5, 4, 3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Bac</t>
+        </is>
+      </c>
       <c r="N21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -1988,15 +2060,19 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>3, 7, 2, 5, 6, 4, 1</t>
+          <t>Auto-Increment</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr"/>
       <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="N22" s="3" t="inlineStr"/>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -2038,15 +2114,19 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>STC, STC-P1, STNMT, STNMT-P1, STNMT-P2, SYT, UBND</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
       <c r="N23" s="3" t="inlineStr"/>
     </row>
-    <row r="24" ht="45" customHeight="1">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -2084,14 +2164,14 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>UBND Tỉnh, Sở Tài nguyên Môi trường, Sở Tài chính, Sở Y tế, Phòng Đất đai, Phòng Khoáng sản, Phòng Ngân sách</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Họ và tên</t>
+          <t>Ten</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
@@ -2134,12 +2214,16 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1, 2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Cap</t>
+        </is>
+      </c>
       <c r="N25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -2180,12 +2264,16 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>STNMT, STC</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr"/>
       <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>MaCha</t>
+        </is>
+      </c>
       <c r="N26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -2228,10 +2316,18 @@
           <t>PK</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Increment</t>
+        </is>
+      </c>
       <c r="K27" s="3" t="inlineStr"/>
       <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="N27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -2259,7 +2355,11 @@
           <t>enum</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Có</t>
@@ -2273,7 +2373,11 @@
       </c>
       <c r="K28" s="3" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>CapDo</t>
+        </is>
+      </c>
       <c r="N28" s="3" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -2314,12 +2418,16 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>AUTH, EXPORT, DB, CRAWL</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
       <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>ModuleName</t>
+        </is>
+      </c>
       <c r="N29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
@@ -2358,10 +2466,18 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
       <c r="K30" s="3" t="inlineStr"/>
       <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Msg</t>
+        </is>
+      </c>
       <c r="N30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -2402,12 +2518,16 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.10, 192.168.1.15, 10.0.0.1, 127.0.0.1</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Ip</t>
+        </is>
+      </c>
       <c r="N31" s="3" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -2448,12 +2568,16 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>1, 2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Uid</t>
+        </is>
+      </c>
       <c r="N32" s="3" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -2492,10 +2616,18 @@
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K33" s="3" t="inlineStr"/>
       <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Ts</t>
+        </is>
+      </c>
       <c r="N33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -2540,12 +2672,16 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>420302, 420101, 420301</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr"/>
       <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>MaVung</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -2590,12 +2726,16 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>CLN, LUA, ODT, ONT, SKK, TMD</t>
+          <t>Map với loai_dat</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>MaLoaiDat</t>
+        </is>
+      </c>
       <c r="N35" s="3" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -2640,12 +2780,16 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
       <c r="N36" s="3" t="inlineStr"/>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -2684,10 +2828,18 @@
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>&gt; 0</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>GiaMin</t>
+        </is>
+      </c>
       <c r="N37" s="3" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -2726,10 +2878,18 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>&gt; 0</t>
+        </is>
+      </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>GiaMax</t>
+        </is>
+      </c>
       <c r="N38" s="3" t="inlineStr"/>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2768,10 +2928,18 @@
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0.50 - 3.00</t>
+        </is>
+      </c>
       <c r="K39" s="3" t="inlineStr"/>
       <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>HeSo</t>
+        </is>
+      </c>
       <c r="N39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2810,10 +2978,18 @@
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="K40" s="3" t="inlineStr"/>
       <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>HieuLuc</t>
+        </is>
+      </c>
       <c r="N40" s="3" t="inlineStr"/>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2852,10 +3028,18 @@
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="K41" s="3" t="inlineStr"/>
       <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>HetHieuLuc</t>
+        </is>
+      </c>
       <c r="N41" s="3" t="inlineStr"/>
     </row>
     <row r="42" ht="15" customHeight="1">
@@ -2894,10 +3078,18 @@
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K42" s="3" t="inlineStr"/>
       <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>UpdatedAt</t>
+        </is>
+      </c>
       <c r="N42" s="3" t="inlineStr"/>
     </row>
     <row r="43" ht="15" customHeight="1">
@@ -2940,10 +3132,18 @@
           <t>PK</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Increment</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="N43" s="3" t="inlineStr"/>
     </row>
     <row r="44" ht="15" customHeight="1">
@@ -2984,12 +3184,16 @@
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>420101, 420102, 420301, 420302</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr"/>
       <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>AreaCode</t>
+        </is>
+      </c>
       <c r="N44" s="3" t="inlineStr"/>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3034,12 +3238,16 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>CLN, LUA, ODT, ONT, SKK, TMD</t>
+          <t>Map với loai_dat</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>MaLoaiDat</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr"/>
     </row>
     <row r="46" ht="15" customHeight="1">
@@ -3074,10 +3282,18 @@
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>DienTich</t>
+        </is>
+      </c>
       <c r="N46" s="3" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
@@ -3116,10 +3332,18 @@
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K47" s="3" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>GiaGd</t>
+        </is>
+      </c>
       <c r="N47" s="3" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
@@ -3160,12 +3384,16 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Mua bán, Chuyển nhượng, Tặng cho</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr"/>
       <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>TransactionType</t>
+        </is>
+      </c>
       <c r="N48" s="3" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
@@ -3206,14 +3434,14 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2, 1, 0</t>
+          <t>0, 1, 2</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái</t>
+          <t>TrangThai</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr"/>
@@ -3254,10 +3482,18 @@
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="K50" s="3" t="inlineStr"/>
       <c r="L50" s="3" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>NgayGd</t>
+        </is>
+      </c>
       <c r="N50" s="3" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
@@ -3296,10 +3532,18 @@
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
       <c r="K51" s="3" t="inlineStr"/>
       <c r="L51" s="3" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>GhiChu</t>
+        </is>
+      </c>
       <c r="N51" s="3" t="inlineStr"/>
     </row>
     <row r="52" ht="15" customHeight="1">
@@ -3340,12 +3584,16 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>admin, user1, user2</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr"/>
       <c r="L52" s="3" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
       <c r="N52" s="3" t="inlineStr"/>
     </row>
     <row r="53" ht="15" customHeight="1">
@@ -3384,10 +3632,18 @@
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K53" s="3" t="inlineStr"/>
       <c r="L53" s="3" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>CreatedAt</t>
+        </is>
+      </c>
       <c r="N53" s="3" t="inlineStr"/>
     </row>
     <row r="54" ht="15" customHeight="1">
@@ -3432,15 +3688,19 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>CLN, LUA, ODT, ONT, SKK, TMD</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr"/>
       <c r="L54" s="3" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
       <c r="N54" s="3" t="inlineStr"/>
     </row>
-    <row r="55" ht="45" customHeight="1">
+    <row r="55" ht="15" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
@@ -3478,14 +3738,14 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Đất cây lâu năm, Đất trồng lúa, Đất ở đô thị, Đất ở nông thôn, Đất đồi núi chưa dùng, Đất thương mại DV</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Họ và tên</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr"/>
@@ -3528,12 +3788,16 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>GroupId</t>
+        </is>
+      </c>
       <c r="N56" s="3" t="inlineStr"/>
     </row>
     <row r="57" ht="15" customHeight="1">
@@ -3574,12 +3838,16 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>FILE_A, FILE_B</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Src</t>
+        </is>
+      </c>
       <c r="N57" s="3" t="inlineStr"/>
     </row>
     <row r="58" ht="15" customHeight="1">
@@ -3620,12 +3888,16 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>0, 1, 2</t>
+          <t>0: Trong hạn, 1: Quá hạn</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>TrangThai</t>
+        </is>
+      </c>
       <c r="N58" s="3" t="inlineStr"/>
     </row>
     <row r="59" ht="15" customHeight="1">
@@ -3666,12 +3938,16 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>420101, 420102, ERR, 420301</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Val1</t>
+        </is>
+      </c>
       <c r="N59" s="3" t="inlineStr"/>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -3712,12 +3988,16 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>ODT, LUA, ONT</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Val2</t>
+        </is>
+      </c>
       <c r="N60" s="3" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
@@ -3758,12 +4038,16 @@
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2024-03-15, 2024-04-01, 2024-05-10</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Val3</t>
+        </is>
+      </c>
       <c r="N61" s="3" t="inlineStr"/>
     </row>
     <row r="62" ht="15" customHeight="1">
@@ -3804,12 +4088,16 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>TXN001, TXN002, TXN003</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr"/>
       <c r="L62" s="3" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>ChucDanh</t>
+        </is>
+      </c>
       <c r="N62" s="3" t="inlineStr"/>
     </row>
     <row r="63" ht="15" customHeight="1">
@@ -3848,10 +4136,18 @@
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K63" s="3" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>TsIn</t>
+        </is>
+      </c>
       <c r="N63" s="3" t="inlineStr"/>
     </row>
   </sheetData>

--- a/output_test/data_catalog.xlsx
+++ b/output_test/data_catalog.xlsx
@@ -476,11 +476,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -488,7 +488,7 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="35" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
@@ -585,34 +585,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ma_dvhc + ma_loai_dat + nam_qd</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:40:49</t>
+          <t>2026-06-10 08:55:17</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>dm_chuc_danh</t>
+          <t>bang_khong_co_pk</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
@@ -638,21 +638,17 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
+      <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:40:49</t>
+          <t>2026-06-10 08:55:19</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
@@ -665,20 +661,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>dm_don_vi</t>
+          <t>bang_rong</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
@@ -690,11 +686,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-10 13:40:49</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
@@ -705,34 +697,34 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>sys_log</t>
+          <t>cau_hinh_he_thong</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>khoa_cau_hinh</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:40:49</t>
+          <t>2026-06-10 08:55:19</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
@@ -745,12 +737,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -758,21 +750,21 @@
         <v>9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>ma_vung + land_code + nam</t>
+          <t>ma_dvhc</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:40:50</t>
+          <t>2026-06-10 08:55:16</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr"/>
@@ -785,20 +777,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -812,7 +804,7 @@
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:40:50</t>
+          <t>2026-06-10 08:55:17</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
@@ -825,7 +817,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -835,24 +827,24 @@
       </c>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>ma_loai_dat</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:40:50</t>
+          <t>2026-06-10 08:55:16</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -865,12 +857,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>stg_import_raw</t>
+          <t>nhat_ky_he_thong</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
@@ -878,22 +870,186 @@
         <v>7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:40:50</t>
+          <t>2026-06-10 08:55:19</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 08:55:27</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>chuc_danh</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 08:55:26</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 08:55:26</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>quyen_truy_cap</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>can_bo_id + ma_quyen</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 08:55:27</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -907,11 +1063,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -919,7 +1075,7 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="31" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
@@ -1004,28 +1160,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ma_dvhc</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>char</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>10 chữ số</t>
+          <t>6 ký tự</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1035,19 +1191,19 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>PK,FK</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Auto-Increment</t>
+          <t>Map với don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>MaCoQuan</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr"/>
@@ -1058,18 +1214,18 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ma_cb</t>
+          <t>ma_loai_dat</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1079,7 +1235,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>20 ký tự</t>
+          <t>10 ký tự</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1089,19 +1245,19 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>PK,FK</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Ký tự chữ và số</t>
+          <t>Map với loai_dat</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>MaCanBo</t>
+          <t>MaLoaiDat</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
@@ -1112,28 +1268,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ho_ten</t>
+          <t>nam_qd</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>100 ký tự</t>
+          <t>5 chữ số</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1141,17 +1297,21 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>HoTen</t>
+          <t>NamQd</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr"/>
@@ -1162,46 +1322,46 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ngay_sinh</t>
+          <t>gia_toi_thieu</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>19 chữ số</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>NgaySinh</t>
+          <t>GiaToiThieu</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
@@ -1212,28 +1372,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>gia_toi_da</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>19 chữ số</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1244,14 +1404,14 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Nam, Nữ, Khác</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>GioiTinh</t>
+          <t>GiaToiDa</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr"/>
@@ -1262,46 +1422,46 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>so_cccd</t>
+          <t>he_so_dieu_chinh</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12 ký tự</t>
+          <t>5,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Chuỗi 12 chữ số</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>SoDinhDanh</t>
+          <t>HeSoDieuChinh</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
@@ -1312,18 +1472,18 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sdt</t>
+          <t>so_quyet_dinh</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1333,7 +1493,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15 ký tự</t>
+          <t>50 ký tự</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1344,14 +1504,14 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Số điện thoại</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>SoDienThoai</t>
+          <t>SoQuyetDinh</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -1362,46 +1522,46 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>ngay_hieu_luc</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>date</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100 ký tự</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>NgayHieuLuc</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
@@ -1412,50 +1572,46 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>don_vi_id</t>
+          <t>ngay_het_hieu_luc</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>date</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5 chữ số</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Map với dm_don_vi</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>MaCoQuan</t>
+          <t>NgayHetHieuLuc</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
@@ -1466,18 +1622,18 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ma_cd</t>
+          <t>nguon_du_lieu</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1487,7 +1643,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10 ký tự</t>
+          <t>200 ký tự</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1498,14 +1654,14 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Ký tự chữ và số</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MaChucDanh</t>
+          <t>NguonDuLieu</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
@@ -1516,28 +1672,28 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_gia_dat</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>trinh_do</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1548,14 +1704,14 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>TC, CD, DH, ThS, TS</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>TrinhDo</t>
+          <t>UpdatedAt</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr"/>
@@ -1566,18 +1722,18 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_khong_co_pk</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>chuyen_nganh</t>
+          <t>ma_tham_chieu</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1587,7 +1743,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>200 ký tự</t>
+          <t>50 ký tự</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1598,14 +1754,14 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>ChuyenNganh</t>
+          <t>MaThamChieu</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
@@ -1616,28 +1772,28 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_khong_co_pk</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>ngay_vao</t>
+          <t>gia_tri_thap</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1648,14 +1804,14 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>NgayVao</t>
+          <t>GiaTriThap</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr"/>
@@ -1666,46 +1822,42 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_khong_co_pk</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>trang_thai</t>
+          <t>gia_tri_cao</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>tinyint</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>3 chữ số</t>
-        </is>
-      </c>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0: Nghỉ, 1: Đang làm</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>TrangThai</t>
+          <t>GiaTriCao</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
@@ -1716,28 +1868,28 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_khong_co_pk</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>luong_cb</t>
+          <t>ghi_chu</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,2</t>
+          <t>255 ký tự</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1748,14 +1900,14 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>LuongCanBo</t>
+          <t>GhiChu</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr"/>
@@ -1766,28 +1918,28 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>can_bo</t>
+          <t>bang_rong</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>int</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD HH:MM:SS</t>
+          <t>10 chữ số</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1795,17 +1947,21 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Auto-Increment</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>UpdatedAt</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
@@ -1816,28 +1972,28 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>dm_chuc_danh</t>
+          <t>bang_rong</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ten</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>tinyint</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3 chữ số</t>
+          <t>100 ký tự</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1845,21 +2001,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Auto-Increment</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Ten</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
@@ -1870,28 +2022,28 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>dm_chuc_danh</t>
+          <t>bang_rong</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>ngay_tao</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10 ký tự</t>
+          <t>YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1899,21 +2051,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Ký tự chữ và số</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>NgayTao</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
@@ -1924,28 +2072,28 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>dm_chuc_danh</t>
+          <t>bang_rong</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ten</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>100 ký tự</t>
+          <t>YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1956,14 +2104,14 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr"/>
       <c r="L20" s="3" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Ten</t>
+          <t>UpdatedAt</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -1974,46 +2122,50 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>dm_chuc_danh</t>
+          <t>cau_hinh_he_thong</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>bac</t>
+          <t>khoa_cau_hinh</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>tinyint</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3 chữ số</t>
+          <t>100 ký tự</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Bac</t>
+          <t>KhoaCauHinh</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
@@ -2024,28 +2176,28 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>dm_don_vi</t>
+          <t>cau_hinh_he_thong</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>gia_tri</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>text</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5 chữ số</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2053,21 +2205,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Auto-Increment</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr"/>
       <c r="L22" s="3" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>GiaTri</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr"/>
@@ -2078,18 +2226,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>dm_don_vi</t>
+          <t>cau_hinh_he_thong</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>kieu_du_lieu</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2107,21 +2255,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Ký tự chữ và số</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>KieuDuLieu</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
@@ -2132,46 +2276,46 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>dm_don_vi</t>
+          <t>cau_hinh_he_thong</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ten</t>
+          <t>meta_json</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>json</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>200 ký tự</t>
+          <t>json</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Ten</t>
+          <t>MetaJson</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
@@ -2182,18 +2326,18 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>dm_don_vi</t>
+          <t>cau_hinh_he_thong</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>cap</t>
+          <t>bat_buoc</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2221,7 +2365,7 @@
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Cap</t>
+          <t>BatBuoc</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
@@ -2232,18 +2376,18 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>dm_don_vi</t>
+          <t>cau_hinh_he_thong</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ma_cha</t>
+          <t>mo_ta</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2253,7 +2397,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20 ký tự</t>
+          <t>500 ký tự</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2264,14 +2408,14 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Ký tự chữ và số</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr"/>
       <c r="L26" s="3" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>MaCha</t>
+          <t>MoTa</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr"/>
@@ -2282,28 +2426,28 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>sys_log</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ma_dvhc</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>char</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19 chữ số</t>
+          <t>6 ký tự</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2318,14 +2462,14 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Auto-Increment</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr"/>
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>MaCoQuan</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr"/>
@@ -2336,28 +2480,28 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>sys_log</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>lvl</t>
+          <t>ten_dvhc</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>200 ký tự</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2368,14 +2512,14 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>DEBUG, INFO, WARN, ERROR, FATAL</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>CapDo</t>
+          <t>TenDvhc</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr"/>
@@ -2386,28 +2530,28 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>sys_log</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>module_name</t>
+          <t>cap_dvhc</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>tinyint</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>50 ký tự</t>
+          <t>3 chữ số</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2418,14 +2562,14 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>ModuleName</t>
+          <t>CapDvhc</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
@@ -2436,46 +2580,50 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>sys_log</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>msg</t>
+          <t>ma_dvhc_cha</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>char</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>6 ký tự</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Map với don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr"/>
       <c r="L30" s="3" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Msg</t>
+          <t>MaCoQuan</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
@@ -2486,28 +2634,28 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>sys_log</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ip</t>
+          <t>dien_tich_km2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>45 ký tự</t>
+          <t>10,2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2518,14 +2666,14 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Ip</t>
+          <t>DienTichKm2</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
@@ -2536,18 +2684,18 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>sys_log</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>uid</t>
+          <t>dan_so</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2575,7 +2723,7 @@
       <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Uid</t>
+          <t>DanSo</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr"/>
@@ -2586,46 +2734,46 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ql_nhan_su</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>sys_log</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ts</t>
+          <t>ghi_chu</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>text</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD HH:MM:SS</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr"/>
       <c r="L33" s="3" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Ts</t>
+          <t>GhiChu</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
@@ -2636,28 +2784,28 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ma_vung</t>
+          <t>ngay_tao</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6 ký tự</t>
+          <t>YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2665,21 +2813,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Ký tự chữ và số</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr"/>
       <c r="L34" s="3" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>MaVung</t>
+          <t>NgayTao</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr"/>
@@ -2690,28 +2834,28 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>don_vi_hanh_chinh</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>land_code</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10 ký tự</t>
+          <t>YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2719,21 +2863,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>PK,FK</t>
-        </is>
-      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Map với loai_dat</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>MaLoaiDat</t>
+          <t>UpdatedAt</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr"/>
@@ -2744,28 +2884,28 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>nam</t>
+          <t>id</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>5 chữ số</t>
+          <t>19 chữ số</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2780,14 +2920,14 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Auto-Increment</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr"/>
@@ -2798,28 +2938,28 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>gia_min</t>
+          <t>ma_dvhc</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>char</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>19 chữ số</t>
+          <t>6 ký tự</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2827,17 +2967,21 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>&gt; 0</t>
+          <t>Map với bang_gia_dat</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>GiaMin</t>
+          <t>MaCoQuan</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
@@ -2848,28 +2992,28 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>gia_max</t>
+          <t>ma_loai_dat</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>19 chữ số</t>
+          <t>10 ký tự</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2877,17 +3021,21 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>&gt; 0</t>
+          <t>Map với bang_gia_dat</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>GiaMax</t>
+          <t>MaLoaiDat</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr"/>
@@ -2898,28 +3046,28 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>he_so</t>
+          <t>nam_qd</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>5 chữ số</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2927,17 +3075,21 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0.50 - 3.00</t>
+          <t>Map với bang_gia_dat</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr"/>
       <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>HeSo</t>
+          <t>NamQd</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
@@ -2948,30 +3100,26 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>hieu_luc</t>
+          <t>dien_tich_m2</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Có</t>
@@ -2980,14 +3128,14 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr"/>
       <c r="L40" s="3" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>HieuLuc</t>
+          <t>DienTichM2</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr"/>
@@ -2998,46 +3146,46 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>het_hieu_luc</t>
+          <t>gia_giao_dich</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>19 chữ số</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr"/>
       <c r="L41" s="3" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>HetHieuLuc</t>
+          <t>GiaGiaoDich</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
@@ -3048,28 +3196,28 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>bang_gia</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>ngay_giao_dich</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>date</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD HH:MM:SS</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3080,14 +3228,14 @@
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr"/>
       <c r="L42" s="3" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>UpdatedAt</t>
+          <t>NgayGiaoDich</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr"/>
@@ -3098,28 +3246,28 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>loai_giao_dich</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>19 chữ số</t>
+          <t>50 ký tự</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3127,21 +3275,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Auto-Increment</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>LoaiGiaoDich</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr"/>
@@ -3152,46 +3296,46 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>area_code</t>
+          <t>ghi_chu</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>mediumtext</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>6 ký tự</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Ký tự chữ và số</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr"/>
       <c r="L44" s="3" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>AreaCode</t>
+          <t>GhiChu</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr"/>
@@ -3202,18 +3346,18 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>land_code</t>
+          <t>tao_boi</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3223,29 +3367,25 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>10 ký tự</t>
+          <t>100 ký tự</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Map với loai_dat</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>MaLoaiDat</t>
+          <t>TaoBoi</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
@@ -3256,26 +3396,30 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>dien_tich</t>
+          <t>ngay_tao</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD HH:MM:SS</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Có</t>
@@ -3291,7 +3435,7 @@
       <c r="L46" s="3" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>DienTich</t>
+          <t>NgayTao</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr"/>
@@ -3302,28 +3446,28 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>lich_su_giao_dich</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>gia_gd</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>19 chữ số</t>
+          <t>YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3341,7 +3485,7 @@
       <c r="L47" s="3" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>GiaGd</t>
+          <t>UpdatedAt</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr"/>
@@ -3352,18 +3496,18 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>loai_dat</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>transaction_type</t>
+          <t>ma_loai_dat</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3373,7 +3517,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>20 ký tự</t>
+          <t>10 ký tự</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3381,17 +3525,21 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr"/>
       <c r="L48" s="3" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>TransactionType</t>
+          <t>MaLoaiDat</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr"/>
@@ -3402,28 +3550,28 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>loai_dat</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>ten_loai_dat</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>tinyint</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3 chữ số</t>
+          <t>100 ký tự</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3434,14 +3582,14 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>0, 1, 2</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>TrangThai</t>
+          <t>MaLoaiDat</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr"/>
@@ -3452,28 +3600,28 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>loai_dat</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>ngay_gd</t>
+          <t>nhom_dat</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>ENUM(3 giá trị)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3484,14 +3632,14 @@
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>Nông nghiệp, Phi nông nghiệp, Chưa sử dụng</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr"/>
       <c r="L50" s="3" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>NgayGd</t>
+          <t>NhomDat</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr"/>
@@ -3502,28 +3650,28 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>loai_dat</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ghi_chu</t>
+          <t>nam_ap_dung</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>year</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>year</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3534,14 +3682,14 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr"/>
       <c r="L51" s="3" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>GhiChu</t>
+          <t>NamApDung</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr"/>
@@ -3552,28 +3700,28 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>loai_dat</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>mo_ta</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>longtext</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>50 ký tự</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3591,7 +3739,7 @@
       <c r="L52" s="3" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>CreatedBy</t>
+          <t>MoTa</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr"/>
@@ -3602,28 +3750,28 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>land_transaction</t>
+          <t>nhat_ky_he_thong</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD HH:MM:SS</t>
+          <t>19 chữ số</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3631,17 +3779,21 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Auto-Increment</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr"/>
       <c r="L53" s="3" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr"/>
@@ -3652,28 +3804,28 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>loai_dat</t>
+          <t>nhat_ky_he_thong</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>cap_do</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>10 ký tự</t>
+          <t>ENUM(5 giá trị)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3681,21 +3833,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Ký tự chữ và số</t>
+          <t>DEBUG, INFO, WARNING, ERROR, CRITICAL</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr"/>
       <c r="L54" s="3" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>CapDo</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr"/>
@@ -3706,18 +3854,18 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>loai_dat</t>
+          <t>nhat_ky_he_thong</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>ma_module</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3727,7 +3875,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>100 ký tự</t>
+          <t>50 ký tự</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3738,14 +3886,14 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>MaModule</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr"/>
@@ -3756,28 +3904,28 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>loai_dat</t>
+          <t>nhat_ky_he_thong</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>group_id</t>
+          <t>thong_diep</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>tinyint</t>
+          <t>tinytext</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>3 chữ số</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3788,14 +3936,14 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>GroupId</t>
+          <t>ThongDiep</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr"/>
@@ -3806,28 +3954,28 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>stg_import_raw</t>
+          <t>nhat_ky_he_thong</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>src</t>
+          <t>du_lieu_raw</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>blob</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>50 ký tự</t>
+          <t>blob</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3838,14 +3986,14 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Src</t>
+          <t>DuLieuRaw</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr"/>
@@ -3856,28 +4004,28 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>stg_import_raw</t>
+          <t>nhat_ky_he_thong</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sts</t>
+          <t>ip_nguon</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>tinyint</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>3 chữ số</t>
+          <t>45 ký tự</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3888,14 +4036,14 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>0: Trong hạn, 1: Quá hạn</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>TrangThai</t>
+          <t>IpNguon</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr"/>
@@ -3906,46 +4054,46 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>gia_dat_ha_tinh</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>stg_import_raw</t>
+          <t>nhat_ky_he_thong</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>val1</t>
+          <t>ngay_tao</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>500 ký tự</t>
+          <t>YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Val1</t>
+          <t>NgayTao</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr"/>
@@ -3956,46 +4104,50 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>quan_ly_can_bo</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>stg_import_raw</t>
+          <t>can_bo</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>val2</t>
+          <t>id</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>mediumint</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>500 ký tự</t>
+          <t>7 chữ số</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Auto-Increment</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Val2</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr"/>
@@ -4006,18 +4158,18 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>quan_ly_can_bo</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>stg_import_raw</t>
+          <t>can_bo</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>val3</t>
+          <t>ma_can_bo</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -4027,25 +4179,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>500 ký tự</t>
+          <t>20 ký tự</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Ký tự chữ và số</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Val3</t>
+          <t>MaCanBo</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr"/>
@@ -4056,18 +4212,18 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>quan_ly_can_bo</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>stg_import_raw</t>
+          <t>can_bo</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>cd</t>
+          <t>ho_ten</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4077,12 +4233,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>20 ký tự</t>
+          <t>100 ký tự</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -4095,7 +4251,7 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>ChucDanh</t>
+          <t>HoTen</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
@@ -4106,49 +4262,1789 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ql_dat_dai</t>
+          <t>quan_ly_can_bo</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>stg_import_raw</t>
+          <t>can_bo</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>ts_in</t>
+          <t>ngay_sinh</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>date</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD HH:MM:SS</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>TsIn</t>
+          <t>NgaySinh</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>gioi_tinh</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>tinyint</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>3 chữ số</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr"/>
+      <c r="L64" s="3" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>GioiTinh</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>so_cccd</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>12 ký tự</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Chuỗi 12 chữ số</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>SoDinhDanh</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>so_dien_thoai</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>15 ký tự</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Số điện thoại</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>SoDienThoai</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>email_ca_nhan</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>100 ký tự</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
+      <c r="L67" s="3" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>email_cong_vu</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>100 ký tự</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>don_vi_id</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>10 chữ số</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Map với don_vi</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr"/>
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>MaCoQuan</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>chuc_danh_id</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>10 chữ số</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Map với chuc_danh</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>ChucDanhId</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>trinh_do_hv</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>ENUM(5 giá trị)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Trung cấp, Cao đẳng, Đại học, Thạc sĩ, Tiến sĩ</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr"/>
+      <c r="L71" s="3" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>TrinhDoHv</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>chuyen_nganh</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>200 ký tự</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>ChuyenNganh</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>ngay_vao_nganh</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr"/>
+      <c r="L73" s="3" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>NgayVaoNganh</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>trang_thai</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>tinyint</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>3 chữ số</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0: Nghỉ, 1: Đang làm</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>TrangThai</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>can_bo</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD HH:MM:SS</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>UpdatedAt</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>chuc_danh</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>10 chữ số</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Increment</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>chuc_danh</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>ma_chuc_danh</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>20 ký tự</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Ký tự chữ và số</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>MaChucDanh</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>chuc_danh</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ten_chuc_danh</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>100 ký tự</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>TenChucDanh</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>chuc_danh</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>cap_bac_toi_thieu</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>tinyint</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>3 chữ số</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>CapBacToiThieu</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>10 chữ số</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Increment</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>ma_don_vi</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>20 ký tự</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Ký tự chữ và số</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr"/>
+      <c r="L81" s="3" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>MaDonVi</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>ten_don_vi</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>200 ký tự</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr"/>
+      <c r="L82" s="3" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>TenDonVi</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>ten_viet_tat</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>50 ký tự</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr"/>
+      <c r="L83" s="3" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>TenVietTat</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>cap_don_vi</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>smallint</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>5 chữ số</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>CapDonVi</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>don_vi_cha_id</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>10 chữ số</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Map với don_vi</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr"/>
+      <c r="L85" s="3" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>MaCoQuan</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>dia_chi</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>500 ký tự</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>DiaChi</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>so_dien_thoai</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>20 ký tự</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Số điện thoại</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>SoDienThoai</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>email_don_vi</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>100 ký tự</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr"/>
+      <c r="L88" s="3" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>ngay_thanh_lap</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr"/>
+      <c r="L89" s="3" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>NgayThanhLap</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>con_hoat_dong</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>tinyint</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>3 chữ số</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>ConHoatDong</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD HH:MM:SS</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr"/>
+      <c r="L91" s="3" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>UpdatedAt</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>quyen_truy_cap</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>can_bo_id</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>mediumint</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>7 chữ số</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>PK,FK</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Map với can_bo</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>CanBoId</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>quyen_truy_cap</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>ma_quyen</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>50 ký tự</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Ký tự chữ và số</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>MaCoQuan</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>quyen_truy_cap</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>pham_vi</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>SET(5 giá trị)</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>READ, WRITE, DELETE, EXPORT, ADMIN</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>PhamVi</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>quyen_truy_cap</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>ngay_cap</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD HH:MM:SS</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>NgayCap</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>quyen_truy_cap</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>ngay_het_han</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD HH:MM:SS</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>NgayHetHan</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>quan_ly_can_bo</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>quyen_truy_cap</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>cap_boi</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>100 ký tự</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr"/>
+      <c r="L97" s="3" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>CapBoi</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_test/data_catalog.xlsx
+++ b/output_test/data_catalog.xlsx
@@ -612,7 +612,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr"/>
@@ -652,7 +652,7 @@
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
@@ -692,7 +692,7 @@
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr"/>
@@ -723,7 +723,7 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
@@ -928,7 +928,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>don_vi_tinh IN (Vien, Vi, Hop, Chai</t>
+          <t>don_vi_tinh IN (Vien, Vi, Hop, Chai)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
